--- a/Sensitivity_PSNR_Couple.xlsx
+++ b/Sensitivity_PSNR_Couple.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6188A0A7-CF5E-40FC-907B-A3318CF030FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C8296E2-B99C-46B0-A1D8-D0FE3B02E0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24AB4AB0-CEE7-4263-8AFD-25E9F722D271}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0AB917DF-0CB0-4EC1-BADB-73602E5D8A3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -442,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19E1E1CE-1E1E-4DC5-AB15-800F8D778A6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C518DA83-AC39-4974-BA71-D1B04BB5DE5B}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -576,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F94AD2B2-80EC-4435-B9D4-DFC0DBC6ED39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{724F43CA-7F61-4768-8CB5-75F769AF4A7D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -585,7 +588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5F83E4-CAE5-41E5-BB97-EC2ED755B6E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF89022F-B8C5-4525-972C-9EE848BDD6D1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
